--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_06/pre_sizing_results_optimized.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_06/pre_sizing_results_optimized.xlsx
@@ -497,2052 +497,2052 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99.99987090488781</v>
+        <v>52.36706380008528</v>
       </c>
       <c r="B2" t="n">
-        <v>72.15451343646306</v>
+        <v>32.20196361610991</v>
       </c>
       <c r="C2" t="n">
-        <v>45.94077692618907</v>
+        <v>26.71965106636539</v>
       </c>
       <c r="D2" t="n">
-        <v>8.911487431051073</v>
+        <v>5.000049545877295</v>
       </c>
       <c r="E2" t="n">
-        <v>2.791733482982845</v>
+        <v>2.838669016199924</v>
       </c>
       <c r="F2" t="n">
-        <v>10.82791357333518</v>
+        <v>5.089167025173537</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01368319545961957</v>
+        <v>0.1355154174974358</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.8667997067883871</v>
+        <v>-0.0008493821818890155</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9336076830053626</v>
+        <v>-0.5963430546182884</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.9722787550766276</v>
+        <v>-0.6009217979306706</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.006398943000715073</v>
+        <v>-0.3468612123925892</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.6220060086445464</v>
+        <v>-0.01005157559675951</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.00239114876411897</v>
+        <v>-0.1225910643791671</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99.99987090488781</v>
+        <v>99.99999980949727</v>
       </c>
       <c r="B3" t="n">
-        <v>74.9352826096294</v>
+        <v>52.13216031305901</v>
       </c>
       <c r="C3" t="n">
-        <v>45.94077692618907</v>
+        <v>45.63040619454286</v>
       </c>
       <c r="D3" t="n">
-        <v>8.911487431051073</v>
+        <v>9.916354808042893</v>
       </c>
       <c r="E3" t="n">
-        <v>2.512505289176373</v>
+        <v>2.713749023488174</v>
       </c>
       <c r="F3" t="n">
-        <v>10.82791357333518</v>
+        <v>11.0537321971572</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01368319545961957</v>
+        <v>0.01346024067758135</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8667997067883871</v>
+        <v>-0.8478747807284841</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9336076830053626</v>
+        <v>-0.9237217243610575</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9722787550766276</v>
+        <v>-0.9669898382722841</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.006398943000715073</v>
+        <v>-0.009209919751896752</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6220060086445464</v>
+        <v>-0.5874999986426681</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.00239114876411897</v>
+        <v>-0.001235701609795525</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>50.0565129808774</v>
+        <v>52.36706380008528</v>
       </c>
       <c r="B4" t="n">
-        <v>62.25937300521064</v>
+        <v>30.70527477096456</v>
       </c>
       <c r="C4" t="n">
-        <v>30.59771706263513</v>
+        <v>26.71965106636539</v>
       </c>
       <c r="D4" t="n">
-        <v>5.000010962882786</v>
+        <v>5.000049545877295</v>
       </c>
       <c r="E4" t="n">
-        <v>2.344549947624847</v>
+        <v>2.771828671687671</v>
       </c>
       <c r="F4" t="n">
-        <v>4.690470938133339</v>
+        <v>5.089167025173537</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1645031433297194</v>
+        <v>0.1355154174974358</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.00205071103919296</v>
+        <v>-0.0008493821818890155</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5959847325113088</v>
+        <v>-0.5963430546182884</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.6008745507005422</v>
+        <v>-0.6009217979306706</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.02246041484576487</v>
+        <v>-0.3468612123925892</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.669314385869643</v>
+        <v>-0.01005157559675951</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.197567727718341</v>
+        <v>-0.1225910643791671</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>55.72833143299902</v>
+        <v>56.68671642321777</v>
       </c>
       <c r="B5" t="n">
-        <v>57.73937030163651</v>
+        <v>53.8374343667023</v>
       </c>
       <c r="C5" t="n">
-        <v>45.93466198109228</v>
+        <v>26.7241780123989</v>
       </c>
       <c r="D5" t="n">
-        <v>5.001558543021622</v>
+        <v>5.000001866992487</v>
       </c>
       <c r="E5" t="n">
-        <v>2.371932599429929</v>
+        <v>2.810679225586824</v>
       </c>
       <c r="F5" t="n">
-        <v>5.33249490407466</v>
+        <v>5.829253997967565</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1097675355103258</v>
+        <v>0.1004000668117544</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2731996011981741</v>
+        <v>-0.2088300484866605</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6885737566506633</v>
+        <v>-0.6660505532900614</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.7380627521590468</v>
+        <v>-0.7072298651837969</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.03291990397403479</v>
+        <v>-0.9649519292285618</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5167799337778514</v>
+        <v>-0.2699561564842226</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.001543580413341971</v>
+        <v>-0.1235719026864286</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>88.10845051594173</v>
+        <v>59.93056637743756</v>
       </c>
       <c r="B6" t="n">
-        <v>144.7930535208163</v>
+        <v>53.93204160033113</v>
       </c>
       <c r="C6" t="n">
-        <v>46.09361027557048</v>
+        <v>45.99077888892759</v>
       </c>
       <c r="D6" t="n">
-        <v>11.42275166203501</v>
+        <v>8.043462926245923</v>
       </c>
       <c r="E6" t="n">
-        <v>2.492470218582229</v>
+        <v>2.818667958183454</v>
       </c>
       <c r="F6" t="n">
-        <v>9.156360204773623</v>
+        <v>5.84515958563323</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02151665925515643</v>
+        <v>0.08318235298357897</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8077698053299043</v>
+        <v>-0.3279412526701778</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9036090047742421</v>
+        <v>-0.7078500509001684</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.9549447230628807</v>
+        <v>-0.7641879299583381</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.04654600916048921</v>
+        <v>-0.0005053893374181369</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5331762691510843</v>
+        <v>-0.3153207409165991</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.01495651276926556</v>
+        <v>-0.08360660318344953</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>53.70318826638535</v>
+        <v>66.37789631840727</v>
       </c>
       <c r="B7" t="n">
-        <v>59.27084626159795</v>
+        <v>40.67691991178913</v>
       </c>
       <c r="C7" t="n">
-        <v>40.73173779337705</v>
+        <v>45.64032398944261</v>
       </c>
       <c r="D7" t="n">
-        <v>5.000007964639416</v>
+        <v>6.569436972751058</v>
       </c>
       <c r="E7" t="n">
-        <v>3.135855529272125</v>
+        <v>2.146669428993155</v>
       </c>
       <c r="F7" t="n">
-        <v>5.131312254649933</v>
+        <v>6.616166893691385</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1261035442853412</v>
+        <v>0.05655143463780629</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1893596383701711</v>
+        <v>-0.5030627300952503</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6594537234629027</v>
+        <v>-0.773527541576158</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6971983881169816</v>
+        <v>-0.842095864744565</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.143099123351096</v>
+        <v>-0.007446504559256632</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.552329231288647</v>
+        <v>-0.05339796206470497</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0734907434873322</v>
+        <v>-0.003502626158312233</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>91.40513620640125</v>
+        <v>63.33579311823748</v>
       </c>
       <c r="B8" t="n">
-        <v>168.9818117122685</v>
+        <v>51.0617349421315</v>
       </c>
       <c r="C8" t="n">
-        <v>45.97016197647896</v>
+        <v>45.74048899398937</v>
       </c>
       <c r="D8" t="n">
-        <v>10.61368689598678</v>
+        <v>7.299914129075287</v>
       </c>
       <c r="E8" t="n">
-        <v>2.522104273406045</v>
+        <v>2.373251491657269</v>
       </c>
       <c r="F8" t="n">
-        <v>9.571197766308352</v>
+        <v>6.242948331994556</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01882914938602982</v>
+        <v>0.06746606012617101</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8272745182461403</v>
+        <v>-0.4292686917345928</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9133036712687477</v>
+        <v>-0.745230816719239</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9609008846134629</v>
+        <v>-0.8102175140006517</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.005736142849765412</v>
+        <v>-0.0007178458151546085</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5578027411365137</v>
+        <v>-0.1769834045716025</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.005822307652837052</v>
+        <v>-0.02639748434042868</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>57.6436358691562</v>
+        <v>81.43824775964183</v>
       </c>
       <c r="B9" t="n">
-        <v>56.11008215801236</v>
+        <v>158.7734623632863</v>
       </c>
       <c r="C9" t="n">
-        <v>40.73159751866472</v>
+        <v>45.8132308530988</v>
       </c>
       <c r="D9" t="n">
-        <v>5.000012798658592</v>
+        <v>12.92191639411938</v>
       </c>
       <c r="E9" t="n">
-        <v>2.792837137930945</v>
+        <v>2.154057659096374</v>
       </c>
       <c r="F9" t="n">
-        <v>5.645303353360648</v>
+        <v>8.381871175951716</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0966269025747951</v>
+        <v>0.02815702806091966</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3422490157293115</v>
+        <v>-0.723227437156167</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7132766561345745</v>
+        <v>-0.8637147894137285</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7705939920905013</v>
+        <v>-0.9270329576732786</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1427284065259382</v>
+        <v>-0.00790387316641257</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.4686677940335797</v>
+        <v>-0.455247515287448</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.07348222511268683</v>
+        <v>-0.04302419499401189</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>80.5645652170782</v>
+        <v>53.59561933525801</v>
       </c>
       <c r="B10" t="n">
-        <v>178.1764907822323</v>
+        <v>41.2662928336792</v>
       </c>
       <c r="C10" t="n">
-        <v>46.15626235267835</v>
+        <v>26.71970800194767</v>
       </c>
       <c r="D10" t="n">
-        <v>12.60502607999837</v>
+        <v>5.000040666224046</v>
       </c>
       <c r="E10" t="n">
-        <v>2.614855324861348</v>
+        <v>2.543100094350582</v>
       </c>
       <c r="F10" t="n">
-        <v>8.164726408984956</v>
+        <v>5.293655203419337</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02985067562848349</v>
+        <v>0.1240984096239163</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7503493802937192</v>
+        <v>-0.06598045822361044</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8762188210595911</v>
+        <v>-0.6178229774556612</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9362850886702656</v>
+        <v>-0.6349694593544334</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.03538571314953443</v>
+        <v>-0.3154410941585825</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4768229199339019</v>
+        <v>-0.405191654082462</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.01882153724389827</v>
+        <v>-0.1226034004219959</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>76.07608897743427</v>
+        <v>83.88044643696048</v>
       </c>
       <c r="B11" t="n">
-        <v>177.3447962224485</v>
+        <v>177.5244078898887</v>
       </c>
       <c r="C11" t="n">
-        <v>45.93469945776317</v>
+        <v>46.1805386671993</v>
       </c>
       <c r="D11" t="n">
-        <v>13.22569426469059</v>
+        <v>12.47364275620702</v>
       </c>
       <c r="E11" t="n">
-        <v>2.320286352847812</v>
+        <v>2.366788206269577</v>
       </c>
       <c r="F11" t="n">
-        <v>7.599441241339374</v>
+        <v>8.70494948464526</v>
       </c>
       <c r="G11" t="n">
-        <v>0.03690863749356049</v>
+        <v>0.02526690157877443</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7046606082114474</v>
+        <v>-0.7461955802182784</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8554252446926889</v>
+        <v>-0.8742401651887789</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9203686195935575</v>
+        <v>-0.9349559176702871</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.02032418471729505</v>
+        <v>-0.001372593914792989</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.4432936894425813</v>
+        <v>-0.4726481808633435</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.001548989719242583</v>
+        <v>-0.1269802667884115</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>62.75485521087933</v>
+        <v>79.01746317976769</v>
       </c>
       <c r="B12" t="n">
-        <v>53.07058498638998</v>
+        <v>188.3978940680261</v>
       </c>
       <c r="C12" t="n">
-        <v>46.18907611143388</v>
+        <v>45.86792711011343</v>
       </c>
       <c r="D12" t="n">
-        <v>7.319090207154058</v>
+        <v>13.27834458225118</v>
       </c>
       <c r="E12" t="n">
-        <v>2.131299481759398</v>
+        <v>2.649811920293208</v>
       </c>
       <c r="F12" t="n">
-        <v>6.242251686014995</v>
+        <v>8.077185190077126</v>
       </c>
       <c r="G12" t="n">
-        <v>0.07119546042003448</v>
+        <v>0.03147550410670192</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4866174533198654</v>
+        <v>-0.6975671128274613</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7668711810060432</v>
+        <v>-0.8521829806335524</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8347764442466675</v>
+        <v>-0.9179198621492082</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1084591579189859</v>
+        <v>-0.0107857538423286</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6256114034468963</v>
+        <v>-0.4379994251558448</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.02044181776622831</v>
+        <v>-0.05552619659735469</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>51.90445289780613</v>
+        <v>77.07997429477376</v>
       </c>
       <c r="B13" t="n">
-        <v>60.76852385614386</v>
+        <v>180.4400527309798</v>
       </c>
       <c r="C13" t="n">
-        <v>29.81698902233844</v>
+        <v>46.80280324116902</v>
       </c>
       <c r="D13" t="n">
-        <v>5.000012387698637</v>
+        <v>13.59110641238621</v>
       </c>
       <c r="E13" t="n">
-        <v>2.84544653252827</v>
+        <v>2.370777846009069</v>
       </c>
       <c r="F13" t="n">
-        <v>4.962810977880492</v>
+        <v>7.889531241768257</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1433332278258134</v>
+        <v>0.03455787603681835</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1036012864343047</v>
+        <v>-0.6745459672212208</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6304081422275883</v>
+        <v>-0.8419930149002066</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.6539285015065751</v>
+        <v>-0.9095141179617575</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.1822444976648939</v>
+        <v>-0.03643085392138527</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6007397319784692</v>
+        <v>-0.4241948168502631</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2271766527513598</v>
+        <v>-0.2692121694100623</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>95.15791216615521</v>
+        <v>67.36777386429195</v>
       </c>
       <c r="B14" t="n">
-        <v>173.7644098612053</v>
+        <v>38.5280207063078</v>
       </c>
       <c r="C14" t="n">
-        <v>45.96084431943574</v>
+        <v>45.77410719891635</v>
       </c>
       <c r="D14" t="n">
-        <v>9.930118738669691</v>
+        <v>6.5431872244353</v>
       </c>
       <c r="E14" t="n">
-        <v>2.58103058825058</v>
+        <v>2.320128954699359</v>
       </c>
       <c r="F14" t="n">
-        <v>10.11286999265613</v>
+        <v>6.781373738804945</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01630788190957553</v>
+        <v>0.05353702436759401</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8462811912815662</v>
+        <v>-0.5242422837611161</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.9229422085410324</v>
+        <v>-0.7818291144210132</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.9664928364780588</v>
+        <v>-0.850965123197467</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.01076078444304116</v>
+        <v>-0.08207827408708632</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5858362392367196</v>
+        <v>-0.01318418676313937</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.004734327150150538</v>
+        <v>-0.03408164546659376</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>61.10649146096893</v>
+        <v>96.56072818996365</v>
       </c>
       <c r="B15" t="n">
-        <v>55.45769721769105</v>
+        <v>39.49603980595689</v>
       </c>
       <c r="C15" t="n">
-        <v>45.95344090813904</v>
+        <v>46.60088150017569</v>
       </c>
       <c r="D15" t="n">
-        <v>7.31587856715576</v>
+        <v>10.55826042706729</v>
       </c>
       <c r="E15" t="n">
-        <v>2.502928870303271</v>
+        <v>2.926481522412699</v>
       </c>
       <c r="F15" t="n">
-        <v>5.974928292219882</v>
+        <v>10.55892595646164</v>
       </c>
       <c r="G15" t="n">
-        <v>0.07864862446281504</v>
+        <v>0.01523521912421837</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.4447388860862523</v>
+        <v>-0.8316158831968298</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7508326903181674</v>
+        <v>-0.9154262625643859</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.8166470550420769</v>
+        <v>-0.9622387289270604</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.001307310213075537</v>
+        <v>-0.03207837603269515</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6223120048056044</v>
+        <v>-0.562995188353491</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.003869864430948105</v>
+        <v>-0.2230586286115861</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>60.23983043054677</v>
+        <v>61.1101648230159</v>
       </c>
       <c r="B16" t="n">
-        <v>55.45370305322199</v>
+        <v>53.98248575224196</v>
       </c>
       <c r="C16" t="n">
-        <v>45.96679977093454</v>
+        <v>46.22833198623609</v>
       </c>
       <c r="D16" t="n">
-        <v>7.316881490354336</v>
+        <v>7.771727584207479</v>
       </c>
       <c r="E16" t="n">
-        <v>2.504088608653643</v>
+        <v>2.542693731295897</v>
       </c>
       <c r="F16" t="n">
-        <v>5.878219103192579</v>
+        <v>5.986237505177355</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0829445014012708</v>
+        <v>0.07725440201747778</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.420900936293137</v>
+        <v>-0.3655997413412759</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7418537042972965</v>
+        <v>-0.7215583094990744</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.8061265977169122</v>
+        <v>-0.7815835362081857</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.002408784588889568</v>
+        <v>-0.001646440507906668</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6081415676945252</v>
+        <v>-0.2673995540649793</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.00542971817874638</v>
+        <v>-0.1379044539968213</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>62.21552166966008</v>
+        <v>95.26212055074437</v>
       </c>
       <c r="B17" t="n">
-        <v>55.17912454428247</v>
+        <v>39.49603980595689</v>
       </c>
       <c r="C17" t="n">
-        <v>46.16818576791334</v>
+        <v>46.60088150017569</v>
       </c>
       <c r="D17" t="n">
-        <v>7.401688483567506</v>
+        <v>10.6144323250303</v>
       </c>
       <c r="E17" t="n">
-        <v>2.569927946113096</v>
+        <v>2.926481522412699</v>
       </c>
       <c r="F17" t="n">
-        <v>6.094571051013916</v>
+        <v>10.33357584708691</v>
       </c>
       <c r="G17" t="n">
-        <v>0.07362849410726055</v>
+        <v>0.01597595390568422</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4732555395669636</v>
+        <v>-0.8248908170626069</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7616813195132156</v>
+        <v>-0.9120578440697297</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.8290263028705761</v>
+        <v>-0.9602302560716737</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.002396216801999725</v>
+        <v>-0.0004844557219584606</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6504512829652147</v>
+        <v>-0.5537426089240537</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.01955709612449373</v>
+        <v>-0.2230586286115861</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>54.53074465657167</v>
+        <v>54.05714583005067</v>
       </c>
       <c r="B18" t="n">
-        <v>58.92457003870029</v>
+        <v>30.70527477096456</v>
       </c>
       <c r="C18" t="n">
-        <v>46.45734272867819</v>
+        <v>26.71966550935638</v>
       </c>
       <c r="D18" t="n">
-        <v>5.001666004047595</v>
+        <v>5.000049545877295</v>
       </c>
       <c r="E18" t="n">
-        <v>2.49863738889214</v>
+        <v>2.548939514374528</v>
       </c>
       <c r="F18" t="n">
-        <v>5.243825306036283</v>
+        <v>5.371699740938392</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1190597192601134</v>
+        <v>0.1201314096081854</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2251345247943488</v>
+        <v>-0.08940427626336894</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6717792525741195</v>
+        <v>-0.625587062209539</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7148172671996976</v>
+        <v>-0.6470869919088645</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2404088372927521</v>
+        <v>-0.4124209549540124</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5331948073206471</v>
+        <v>-0.3849998699352828</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.02963210256890187</v>
+        <v>-0.1225941936938819</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>85.30616269015633</v>
+        <v>56.12669372763188</v>
       </c>
       <c r="B19" t="n">
-        <v>160.586942635326</v>
+        <v>46.44369365370881</v>
       </c>
       <c r="C19" t="n">
-        <v>45.96947426970864</v>
+        <v>26.73136718123915</v>
       </c>
       <c r="D19" t="n">
-        <v>11.71210720419723</v>
+        <v>5.00294015862806</v>
       </c>
       <c r="E19" t="n">
-        <v>2.571398917418399</v>
+        <v>2.331762035784315</v>
       </c>
       <c r="F19" t="n">
-        <v>8.744453718097247</v>
+        <v>5.730683886497381</v>
       </c>
       <c r="G19" t="n">
-        <v>0.02418115818431689</v>
+        <v>0.1042296822681299</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7888201134974391</v>
+        <v>-0.18524678483799</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8944147357154978</v>
+        <v>-0.6579369876099723</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9489685328898652</v>
+        <v>-0.6955769010590866</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.0118030097855718</v>
+        <v>-0.8475174971567041</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5122429836891046</v>
+        <v>-0.2944571494161051</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.005742007256051926</v>
+        <v>-0.1251295559351498</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>57.03280757468178</v>
+        <v>69.32396227693849</v>
       </c>
       <c r="B20" t="n">
-        <v>57.45576631409645</v>
+        <v>33.60026780533685</v>
       </c>
       <c r="C20" t="n">
-        <v>46.15895702894871</v>
+        <v>45.90126119258531</v>
       </c>
       <c r="D20" t="n">
-        <v>5.150104294907687</v>
+        <v>6.509465484878393</v>
       </c>
       <c r="E20" t="n">
-        <v>2.619738847461521</v>
+        <v>2.697928767836034</v>
       </c>
       <c r="F20" t="n">
-        <v>5.509226641255497</v>
+        <v>7.114814781628024</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1007101151581335</v>
+        <v>0.04817275946448765</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3210580497563674</v>
+        <v>-0.5626377543843765</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7055850109299667</v>
+        <v>-0.7971187663800895</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7607049751747945</v>
+        <v>-0.8667110540035803</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.02853321941647432</v>
+        <v>-0.09320592696964332</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.4973953424223529</v>
+        <v>-0.005926493204518324</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.01898777259022556</v>
+        <v>-0.0631454154480704</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>56.37798933010151</v>
+        <v>64.77734499448943</v>
       </c>
       <c r="B21" t="n">
-        <v>57.38563535341692</v>
+        <v>49.16455231357059</v>
       </c>
       <c r="C21" t="n">
-        <v>40.71726640806315</v>
+        <v>45.75917155455775</v>
       </c>
       <c r="D21" t="n">
-        <v>5.023221985370246</v>
+        <v>6.967327374245103</v>
       </c>
       <c r="E21" t="n">
-        <v>2.571459897444393</v>
+        <v>2.697928767836034</v>
       </c>
       <c r="F21" t="n">
-        <v>5.442402029962758</v>
+        <v>6.420729196467497</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1050718382090483</v>
+        <v>0.06198308650329132</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2976625552654537</v>
+        <v>-0.4659597277282788</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6972496858864526</v>
+        <v>-0.7591757575529363</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7497092699091624</v>
+        <v>-0.8262499831781431</v>
       </c>
       <c r="K21" t="n">
-        <v>-8.738608992612622e-06</v>
+        <v>-0.006021266593269046</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5004606317696144</v>
+        <v>-0.1184203595988674</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.07283524316475185</v>
+        <v>-0.03066778389891514</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>64.4463836890248</v>
+        <v>80.38365084009351</v>
       </c>
       <c r="B22" t="n">
-        <v>64.59069168848197</v>
+        <v>166.8403227668307</v>
       </c>
       <c r="C22" t="n">
-        <v>45.96052535629198</v>
+        <v>46.84964430566961</v>
       </c>
       <c r="D22" t="n">
-        <v>7.112413275111463</v>
+        <v>12.88654394201254</v>
       </c>
       <c r="E22" t="n">
-        <v>2.35005874570802</v>
+        <v>2.004098557206901</v>
       </c>
       <c r="F22" t="n">
-        <v>6.356527416294096</v>
+        <v>8.263277800046362</v>
       </c>
       <c r="G22" t="n">
-        <v>0.06452541666895407</v>
+        <v>0.02955396101498875</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5251998797494134</v>
+        <v>-0.7124008918902085</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7819254629051466</v>
+        <v>-0.8588109410978012</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8510427983145293</v>
+        <v>-0.9232185883742169</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.01084433778991216</v>
+        <v>-0.001390264429031175</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6779279822217835</v>
+        <v>-0.4477335122356663</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.004697083272222585</v>
+        <v>-0.2799186984387675</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>78.32301701968196</v>
+        <v>72.01587948126857</v>
       </c>
       <c r="B23" t="n">
-        <v>129.744322360987</v>
+        <v>30.18991498759435</v>
       </c>
       <c r="C23" t="n">
-        <v>45.94575992293455</v>
+        <v>46.19610044082225</v>
       </c>
       <c r="D23" t="n">
-        <v>12.78260618429637</v>
+        <v>6.536287500462898</v>
       </c>
       <c r="E23" t="n">
-        <v>2.473365176305055</v>
+        <v>2.328200554066</v>
       </c>
       <c r="F23" t="n">
-        <v>7.851322312971494</v>
+        <v>7.604303904561799</v>
       </c>
       <c r="G23" t="n">
-        <v>0.03310565588277629</v>
+        <v>0.04189730731659506</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7288805247152313</v>
+        <v>-0.6078901235751148</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8663660991084398</v>
+        <v>-0.8152450532077852</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.928919478412751</v>
+        <v>-0.8845951027097202</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.004723450436899018</v>
+        <v>-0.1722173736432265</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.4600783985963298</v>
+        <v>-0.6392589575407998</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.002972990666958766</v>
+        <v>-0.1305372436165148</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>82.23770190377134</v>
+        <v>55.64887906101982</v>
       </c>
       <c r="B24" t="n">
-        <v>148.9253689593637</v>
+        <v>34.16683563208898</v>
       </c>
       <c r="C24" t="n">
-        <v>40.77071317431817</v>
+        <v>27.7606111296376</v>
       </c>
       <c r="D24" t="n">
-        <v>13.44493514064632</v>
+        <v>5.000100492287057</v>
       </c>
       <c r="E24" t="n">
-        <v>2.400589284400874</v>
+        <v>3.097907882543761</v>
       </c>
       <c r="F24" t="n">
-        <v>8.544998205607405</v>
+        <v>5.676452711440328</v>
       </c>
       <c r="G24" t="n">
-        <v>0.02778617911487668</v>
+        <v>0.1076859281355544</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.7647049594422469</v>
+        <v>-0.1643063013291698</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8828371502298056</v>
+        <v>-0.6507705655218492</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.9410826837563698</v>
+        <v>-0.6851277703563421</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.08070418514945614</v>
+        <v>-0.7562119452573456</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.4893213676512211</v>
+        <v>-0.3153615410803828</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.07490034519629886</v>
+        <v>-0.3481324114214808</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>58.73267598072886</v>
+        <v>62.61264312200527</v>
       </c>
       <c r="B25" t="n">
-        <v>55.36896680017906</v>
+        <v>51.0617349421315</v>
       </c>
       <c r="C25" t="n">
-        <v>46.45734272867819</v>
+        <v>45.74048899398937</v>
       </c>
       <c r="D25" t="n">
-        <v>5.001649600187373</v>
+        <v>7.474135511281585</v>
       </c>
       <c r="E25" t="n">
-        <v>2.49863738889214</v>
+        <v>2.373251491657269</v>
       </c>
       <c r="F25" t="n">
-        <v>5.771528754004406</v>
+        <v>6.157182613403952</v>
       </c>
       <c r="G25" t="n">
-        <v>0.09014425215178656</v>
+        <v>0.07045799865386271</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.3774796237126372</v>
+        <v>-0.4095703022708037</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.726109603304388</v>
+        <v>-0.7378381371317498</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.7867547700273384</v>
+        <v>-0.80146641486638</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.1593733463024317</v>
+        <v>-0.002035675926269504</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.4600613381320067</v>
+        <v>-0.2063613731685356</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.02963210256890187</v>
+        <v>-0.02639748434042868</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>51.78141126650469</v>
+        <v>64.71895000641577</v>
       </c>
       <c r="B26" t="n">
-        <v>61.77594513245642</v>
+        <v>49.16455231357059</v>
       </c>
       <c r="C26" t="n">
-        <v>40.90857488071139</v>
+        <v>45.92221696385429</v>
       </c>
       <c r="D26" t="n">
-        <v>5.000104714515152</v>
+        <v>6.986792435178744</v>
       </c>
       <c r="E26" t="n">
-        <v>2.406032051595722</v>
+        <v>2.697928767836034</v>
       </c>
       <c r="F26" t="n">
-        <v>4.86261453975942</v>
+        <v>6.418534119371714</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1448023140193036</v>
+        <v>0.06219902903545787</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.09706606504873584</v>
+        <v>-0.4645309437667239</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.628143634046569</v>
+        <v>-0.7586267691665002</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.6505465944861082</v>
+        <v>-0.8256317459293184</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.005353376008768203</v>
+        <v>-0.01092347769096444</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.609507040393196</v>
+        <v>-0.1207926559893596</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.07954942030320163</v>
+        <v>-0.06793530602383774</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>92.88398354070728</v>
+        <v>75.95773686046331</v>
       </c>
       <c r="B27" t="n">
-        <v>74.87828346223429</v>
+        <v>184.0371785685973</v>
       </c>
       <c r="C27" t="n">
-        <v>45.97631331667215</v>
+        <v>45.95745450207313</v>
       </c>
       <c r="D27" t="n">
-        <v>11.01475150053082</v>
+        <v>13.6862825382787</v>
       </c>
       <c r="E27" t="n">
-        <v>2.574384093801356</v>
+        <v>2.783359754827426</v>
       </c>
       <c r="F27" t="n">
-        <v>9.892719942869409</v>
+        <v>7.702051104236327</v>
       </c>
       <c r="G27" t="n">
-        <v>0.01781505802231743</v>
+        <v>0.03644756106640616</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.8350454705464764</v>
+        <v>-0.6602922147567984</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.9171772422168535</v>
+        <v>-0.8358280948090832</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.9632077204074619</v>
+        <v>-0.9042231053138974</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.1237979978926813</v>
+        <v>-0.01036513809722515</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.5688498338437161</v>
+        <v>-0.4161988751308011</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.00654057171477144</v>
+        <v>-0.07598960047385972</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>66.03038033595439</v>
+        <v>60.2915472071899</v>
       </c>
       <c r="B28" t="n">
-        <v>55.17912454428247</v>
+        <v>55.22747629167492</v>
       </c>
       <c r="C28" t="n">
-        <v>46.16818576791334</v>
+        <v>45.67538556526267</v>
       </c>
       <c r="D28" t="n">
-        <v>6.695126119570245</v>
+        <v>8.013488494418432</v>
       </c>
       <c r="E28" t="n">
-        <v>2.569927946113096</v>
+        <v>2.126003894704244</v>
       </c>
       <c r="F28" t="n">
-        <v>6.550364259082391</v>
+        <v>5.885633554260394</v>
       </c>
       <c r="G28" t="n">
-        <v>0.05889198891271354</v>
+        <v>0.08130373448804742</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.5580203747003274</v>
+        <v>-0.339782399279621</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.7950217816287342</v>
+        <v>-0.712139300466525</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.8645609698699452</v>
+        <v>-0.7696938918696801</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.009140214491602324</v>
+        <v>-0.005541197387804483</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.6884458181369441</v>
+        <v>-0.3006558947079106</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.01955709612449373</v>
+        <v>-0.01151670063146787</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>52.99069901073595</v>
+        <v>69.91896805734841</v>
       </c>
       <c r="B29" t="n">
-        <v>60.71588985396949</v>
+        <v>36.84304322398835</v>
       </c>
       <c r="C29" t="n">
-        <v>45.94195917118157</v>
+        <v>46.65728559106918</v>
       </c>
       <c r="D29" t="n">
-        <v>5.000006759839119</v>
+        <v>6.569833091585134</v>
       </c>
       <c r="E29" t="n">
-        <v>2.349364898033149</v>
+        <v>2.247514378206638</v>
       </c>
       <c r="F29" t="n">
-        <v>4.988807148101222</v>
+        <v>7.246784052237389</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1327105787532281</v>
+        <v>0.04670194879424523</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1566149654257036</v>
+        <v>-0.5723351139235751</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.6482661066902475</v>
+        <v>-0.8006805715740903</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.6808301434569194</v>
+        <v>-0.8705088116854156</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.0432049609287583</v>
+        <v>-0.03260728290262138</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.5793269707529293</v>
+        <v>-0.6928201310298732</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.002529194143475522</v>
+        <v>-0.2359509922443842</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>81.48806777033489</v>
+        <v>87.07284596867939</v>
       </c>
       <c r="B30" t="n">
-        <v>151.4213575616932</v>
+        <v>187.6021481763493</v>
       </c>
       <c r="C30" t="n">
-        <v>45.96814565411267</v>
+        <v>46.25563983493143</v>
       </c>
       <c r="D30" t="n">
-        <v>13.44493514064632</v>
+        <v>12.12334264133981</v>
       </c>
       <c r="E30" t="n">
-        <v>2.509775191815165</v>
+        <v>2.144867152146732</v>
       </c>
       <c r="F30" t="n">
-        <v>8.435060679195393</v>
+        <v>9.164348227920151</v>
       </c>
       <c r="G30" t="n">
-        <v>0.02872994792486451</v>
+        <v>0.02206587796105493</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.7583326765971624</v>
+        <v>-0.7724439315931165</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.8798544532427406</v>
+        <v>-0.8865199167942689</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.9389583043251021</v>
+        <v>-0.9437212621578625</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.1682010950377929</v>
+        <v>-0.02408180330501954</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.4837215484025073</v>
+        <v>-0.4953940275268407</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.005586870845978044</v>
+        <v>-0.1441462479843264</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>70.21759948585505</v>
+        <v>71.36168376017397</v>
       </c>
       <c r="B31" t="n">
-        <v>57.38101426809595</v>
+        <v>45.0149172188931</v>
       </c>
       <c r="C31" t="n">
-        <v>40.72762969311385</v>
+        <v>45.62978818031947</v>
       </c>
       <c r="D31" t="n">
-        <v>5.887798074231311</v>
+        <v>6.177329071371121</v>
       </c>
       <c r="E31" t="n">
-        <v>2.470541989677435</v>
+        <v>2.103302273089766</v>
       </c>
       <c r="F31" t="n">
-        <v>7.120568065353101</v>
+        <v>7.414144336115704</v>
       </c>
       <c r="G31" t="n">
-        <v>0.04682898754487601</v>
+        <v>0.04327557812506627</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.6311602938685498</v>
+        <v>-0.5973465585267207</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8250927357575895</v>
+        <v>-0.8109264644143859</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.8934737110262346</v>
+        <v>-0.8804697789205135</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.01444856044205695</v>
+        <v>-0.005619957960140557</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.7162492128252105</v>
+        <v>-0.6697880911918813</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.07324127345426118</v>
+        <v>-0.001094441215880038</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>64.88117143290489</v>
+        <v>53.00528418279737</v>
       </c>
       <c r="B32" t="n">
-        <v>64.17867313327241</v>
+        <v>42.10927363072103</v>
       </c>
       <c r="C32" t="n">
-        <v>45.96052535629198</v>
+        <v>26.71970800194767</v>
       </c>
       <c r="D32" t="n">
-        <v>7.025538378079974</v>
+        <v>5.000040666224046</v>
       </c>
       <c r="E32" t="n">
-        <v>2.505971067059342</v>
+        <v>2.365380031907973</v>
       </c>
       <c r="F32" t="n">
-        <v>6.412310279981229</v>
+        <v>5.194804581176269</v>
       </c>
       <c r="G32" t="n">
-        <v>0.06291472800032312</v>
+        <v>0.12942275261076</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.5345234219666236</v>
+        <v>-0.03482123417927396</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.7856208827531418</v>
+        <v>-0.6075760498196995</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.8549150161038107</v>
+        <v>-0.6186938573079146</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.0163828968662878</v>
+        <v>-0.191395306230309</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.6808149997902347</v>
+        <v>-0.4310188170026151</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.004697083272222585</v>
+        <v>-0.1226034004219959</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>53.0095277655787</v>
+        <v>52.53105121538815</v>
       </c>
       <c r="B33" t="n">
-        <v>60.69612439399582</v>
+        <v>30.7172846717676</v>
       </c>
       <c r="C33" t="n">
-        <v>45.94195917118157</v>
+        <v>26.71965106636539</v>
       </c>
       <c r="D33" t="n">
-        <v>5.00898485270188</v>
+        <v>5.000049545877295</v>
       </c>
       <c r="E33" t="n">
-        <v>2.505277219384475</v>
+        <v>2.815834373417726</v>
       </c>
       <c r="F33" t="n">
-        <v>4.993249239088177</v>
+        <v>5.116187817643674</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1325345743692058</v>
+        <v>0.1339152222891013</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.1574975375994958</v>
+        <v>-0.0100656380573411</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6485648448208298</v>
+        <v>-0.5996059814313904</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.6812734934916482</v>
+        <v>-0.6058079172073985</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.04903778603693412</v>
+        <v>-0.3822259656674142</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.5787629542265486</v>
+        <v>-0.003820053815250894</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.002529194143475522</v>
+        <v>-0.1225910643791671</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>95.56427485234536</v>
+        <v>75.21025731672702</v>
       </c>
       <c r="B34" t="n">
-        <v>161.189654662597</v>
+        <v>182.8162351290371</v>
       </c>
       <c r="C34" t="n">
-        <v>46.09054890006455</v>
+        <v>45.78482719753702</v>
       </c>
       <c r="D34" t="n">
-        <v>11.39964138431948</v>
+        <v>13.83934291678136</v>
       </c>
       <c r="E34" t="n">
-        <v>2.656651397336484</v>
+        <v>2.152359285071894</v>
       </c>
       <c r="F34" t="n">
-        <v>10.43359102961171</v>
+        <v>7.612278622294357</v>
       </c>
       <c r="G34" t="n">
-        <v>0.01613988759795944</v>
+        <v>0.0378167047000211</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.8479879323054985</v>
+        <v>-0.6502481283864882</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.9237301675014745</v>
+        <v>-0.8314951689833335</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.9669737200425178</v>
+        <v>-0.9004440297636547</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.2631513207734025</v>
+        <v>-0.01403502836079592</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.5888717968382059</v>
+        <v>-0.4108730833816799</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.01476765564269162</v>
+        <v>-0.03653193086560466</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>58.79556585335186</v>
+        <v>91.36987209703179</v>
       </c>
       <c r="B35" t="n">
-        <v>54.90006744172744</v>
+        <v>182.4780866661116</v>
       </c>
       <c r="C35" t="n">
-        <v>46.45734272867819</v>
+        <v>46.63647408212659</v>
       </c>
       <c r="D35" t="n">
-        <v>5.001649600187373</v>
+        <v>11.86038801663094</v>
       </c>
       <c r="E35" t="n">
-        <v>2.344714843421633</v>
+        <v>2.595095836011707</v>
       </c>
       <c r="F35" t="n">
-        <v>5.85160352665606</v>
+        <v>9.859488122833705</v>
       </c>
       <c r="G35" t="n">
-        <v>0.08971211607346634</v>
+        <v>0.01857755007065752</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.3795398785043713</v>
+        <v>-0.8021980478813909</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7268919541923463</v>
+        <v>-0.9007947389129523</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.7877030422765674</v>
+        <v>-0.9532560172127438</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.368930547063767</v>
+        <v>-0.09944466842201041</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.4397314978871377</v>
+        <v>-0.5260103386913515</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.02963210256890187</v>
+        <v>-0.231194075914649</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>54.34521860740819</v>
+        <v>90.15592655315787</v>
       </c>
       <c r="B36" t="n">
-        <v>58.97143487758134</v>
+        <v>196.5589058250195</v>
       </c>
       <c r="C36" t="n">
-        <v>40.62796656037523</v>
+        <v>46.2028909799058</v>
       </c>
       <c r="D36" t="n">
-        <v>5.000006851980574</v>
+        <v>11.88962208805976</v>
       </c>
       <c r="E36" t="n">
-        <v>2.281174518642722</v>
+        <v>2.306988356956986</v>
       </c>
       <c r="F36" t="n">
-        <v>5.203041063424682</v>
+        <v>9.638151066578136</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1205876501369843</v>
+        <v>0.01947463353268547</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.2173100011200564</v>
+        <v>-0.7943829298320274</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6690723710548336</v>
+        <v>-0.897013843809135</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.7109873038924093</v>
+        <v>-0.9507960695940215</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.1067216743696628</v>
+        <v>-0.06408909588228139</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.5387522517016616</v>
+        <v>-0.5173609766912498</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.06962131221911055</v>
+        <v>-0.1320893668356121</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>66.78156816431679</v>
+        <v>88.86699823023538</v>
       </c>
       <c r="B37" t="n">
-        <v>57.45375486097898</v>
+        <v>182.4780866661116</v>
       </c>
       <c r="C37" t="n">
-        <v>46.08660156218236</v>
+        <v>46.63647408212659</v>
       </c>
       <c r="D37" t="n">
-        <v>6.701815648017548</v>
+        <v>11.86038801663094</v>
       </c>
       <c r="E37" t="n">
-        <v>2.518423408149069</v>
+        <v>2.613562729386107</v>
       </c>
       <c r="F37" t="n">
-        <v>6.673959146211131</v>
+        <v>9.434326820446614</v>
       </c>
       <c r="G37" t="n">
-        <v>0.05647247989906294</v>
+        <v>0.02050388821347171</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.5724706601568872</v>
+        <v>-0.7855831371835923</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8008497731117477</v>
+        <v>-0.8927791741786159</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.8704052955607311</v>
+        <v>-0.9479870743020983</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.06640155628481904</v>
+        <v>-0.03492606255526546</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.6934337518775214</v>
+        <v>-0.5081773623904271</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.01452414324488221</v>
+        <v>-0.231194075914649</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>67.61075243774678</v>
+        <v>88.58644360733689</v>
       </c>
       <c r="B38" t="n">
-        <v>55.45587545624255</v>
+        <v>182.6344467572956</v>
       </c>
       <c r="C38" t="n">
-        <v>45.97713274765988</v>
+        <v>45.68809277970671</v>
       </c>
       <c r="D38" t="n">
-        <v>7.316757777856868</v>
+        <v>11.85337158064006</v>
       </c>
       <c r="E38" t="n">
-        <v>2.505971067059342</v>
+        <v>2.90793403368871</v>
       </c>
       <c r="F38" t="n">
-        <v>6.912006674151465</v>
+        <v>9.345757745842796</v>
       </c>
       <c r="G38" t="n">
-        <v>0.05403688153370591</v>
+        <v>0.02071810119144491</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.5875484781413977</v>
+        <v>-0.7836515885027104</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.80693945654915</v>
+        <v>-0.8918766077141699</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.8764211945728443</v>
+        <v>-0.9473689455785378</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.2676416810612161</v>
+        <v>-0.006497550622494018</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.6989395868477367</v>
+        <v>-0.5061784107022753</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.00663625295028097</v>
+        <v>-0.0144212067901045</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>92.36057670941834</v>
+        <v>54.43004689728625</v>
       </c>
       <c r="B39" t="n">
-        <v>171.5290053586159</v>
+        <v>30.70527477096456</v>
       </c>
       <c r="C39" t="n">
-        <v>45.97016197647896</v>
+        <v>24.27911887727242</v>
       </c>
       <c r="D39" t="n">
-        <v>10.47785482050488</v>
+        <v>5.000020212575867</v>
       </c>
       <c r="E39" t="n">
-        <v>2.522395689827035</v>
+        <v>2.812389017003717</v>
       </c>
       <c r="F39" t="n">
-        <v>9.713004961613665</v>
+        <v>5.473111904511352</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01814201644723693</v>
+        <v>0.1171010298654143</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.832402649691472</v>
+        <v>-0.1076637584300304</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.9158807676367771</v>
+        <v>-0.6316566216016682</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.9624303425606954</v>
+        <v>-0.6564501224089868</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.0133609328331218</v>
+        <v>-0.4397662072142139</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.5649399483168607</v>
+        <v>-0.3686854482437265</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.005822307652837052</v>
+        <v>-0.2790434586040613</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>78.78213940351988</v>
+        <v>68.32200505039093</v>
       </c>
       <c r="B40" t="n">
-        <v>130.2247393054693</v>
+        <v>46.80670012820821</v>
       </c>
       <c r="C40" t="n">
-        <v>45.94591556594222</v>
+        <v>46.2384421957776</v>
       </c>
       <c r="D40" t="n">
-        <v>12.78260618429637</v>
+        <v>6.572502299987769</v>
       </c>
       <c r="E40" t="n">
-        <v>2.465223304784294</v>
+        <v>2.181357912934927</v>
       </c>
       <c r="F40" t="n">
-        <v>7.918811968946804</v>
+        <v>6.959899746290048</v>
       </c>
       <c r="G40" t="n">
-        <v>0.03240544615499256</v>
+        <v>0.05084087099751348</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.733470737514848</v>
+        <v>-0.5435048139879357</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.8684550925375636</v>
+        <v>-0.7894557451889787</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.9305105820315759</v>
+        <v>-0.8589179660289938</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.01557604351071041</v>
+        <v>-0.03977144705134731</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.4635080748181756</v>
+        <v>-0.04558730008869287</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.002991164394210273</v>
+        <v>-0.1402153590348804</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>72.91102811883873</v>
+        <v>70.84657573394404</v>
       </c>
       <c r="B41" t="n">
-        <v>57.73937030163651</v>
+        <v>33.61967251600796</v>
       </c>
       <c r="C41" t="n">
-        <v>45.94288760384532</v>
+        <v>45.62979011294298</v>
       </c>
       <c r="D41" t="n">
-        <v>5.000091846790273</v>
+        <v>6.318247966980454</v>
       </c>
       <c r="E41" t="n">
-        <v>2.344634495312264</v>
+        <v>2.326516167423553</v>
       </c>
       <c r="F41" t="n">
-        <v>7.457416632575061</v>
+        <v>7.345240785821868</v>
       </c>
       <c r="G41" t="n">
-        <v>0.04071949415545521</v>
+        <v>0.04445400385729902</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.6697832119847749</v>
+        <v>-0.5886620000669033</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.8415585449812216</v>
+        <v>-0.8073556124971522</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.9080175111577682</v>
+        <v>-0.8770348491660345</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.1568365770640522</v>
+        <v>-0.007045576368948204</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.7111243066822363</v>
+        <v>-0.6938264657492779</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.002637603009731039</v>
+        <v>-0.001094882958394411</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>97.91315655817748</v>
+        <v>94.12974049388812</v>
       </c>
       <c r="B42" t="n">
-        <v>55.98891845822959</v>
+        <v>34.24984451237821</v>
       </c>
       <c r="C42" t="n">
-        <v>45.94048446079363</v>
+        <v>45.89891536259863</v>
       </c>
       <c r="D42" t="n">
-        <v>9.518970587654389</v>
+        <v>10.4751895930948</v>
       </c>
       <c r="E42" t="n">
-        <v>2.782485927486724</v>
+        <v>2.649811920293208</v>
       </c>
       <c r="F42" t="n">
-        <v>10.54189421662505</v>
+        <v>10.08161727296127</v>
       </c>
       <c r="G42" t="n">
-        <v>0.01474480239721978</v>
+        <v>0.01664418464476277</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.8584353960466309</v>
+        <v>-0.820010723193116</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.9292180102029957</v>
+        <v>-0.9102254567573727</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.96995219543989</v>
+        <v>-0.9588405909677878</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.04028116224704351</v>
+        <v>-0.003305176280238507</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.6064181069681531</v>
+        <v>-0.02563317914694626</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.002356998907941167</v>
+        <v>-0.06260922573682978</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>51.05912103030361</v>
+        <v>55.25773535447621</v>
       </c>
       <c r="B43" t="n">
-        <v>61.67125367988196</v>
+        <v>30.70527477096456</v>
       </c>
       <c r="C43" t="n">
-        <v>30.90263487261292</v>
+        <v>26.71966550935638</v>
       </c>
       <c r="D43" t="n">
-        <v>5.001102080405857</v>
+        <v>5.000049545877295</v>
       </c>
       <c r="E43" t="n">
-        <v>2.621740679413521</v>
+        <v>2.812389017003717</v>
       </c>
       <c r="F43" t="n">
-        <v>4.853383100583146</v>
+        <v>5.577854665605399</v>
       </c>
       <c r="G43" t="n">
-        <v>0.1525278879164574</v>
+        <v>0.1105524548940734</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.05899489448706697</v>
+        <v>-0.1467450684625935</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.6153236258483813</v>
+        <v>-0.6448251160475105</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.6308600807371143</v>
+        <v>-0.6763127244555716</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.2238360315445469</v>
+        <v>-0.6646921636427944</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.6320148292026673</v>
+        <v>-0.3324740782416656</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.2010885905775727</v>
+        <v>-0.1225941936938819</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>98.62382113555556</v>
+        <v>97.94728834529944</v>
       </c>
       <c r="B44" t="n">
-        <v>172.9239460074475</v>
+        <v>178.8295097315608</v>
       </c>
       <c r="C44" t="n">
-        <v>47.31785666853044</v>
+        <v>46.5974709227448</v>
       </c>
       <c r="D44" t="n">
-        <v>9.961085784500046</v>
+        <v>10.62413647748887</v>
       </c>
       <c r="E44" t="n">
-        <v>2.621919446718088</v>
+        <v>2.650355033941866</v>
       </c>
       <c r="F44" t="n">
-        <v>10.79495162869647</v>
+        <v>10.82403058376221</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0144094446854631</v>
+        <v>0.01450002544325413</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.8612729319108988</v>
+        <v>-0.8383951595882803</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.9306543260256981</v>
+        <v>-0.9188411266356288</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.97074144345054</v>
+        <v>-0.9642359606700934</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.1756064098922248</v>
+        <v>-0.08849947896066192</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.6117268209157659</v>
+        <v>-0.5728744294602585</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.02888173207472383</v>
+        <v>-0.2222790680559542</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>50.1194028535004</v>
+        <v>68.20912988221878</v>
       </c>
       <c r="B45" t="n">
-        <v>62.25937300521064</v>
+        <v>38.5280207063078</v>
       </c>
       <c r="C45" t="n">
-        <v>30.59771706263513</v>
+        <v>45.77410719891635</v>
       </c>
       <c r="D45" t="n">
-        <v>5.000010962882786</v>
+        <v>6.5431872244353</v>
       </c>
       <c r="E45" t="n">
-        <v>2.344549947624847</v>
+        <v>2.320128954699359</v>
       </c>
       <c r="F45" t="n">
-        <v>4.700225092170454</v>
+        <v>6.924716372898502</v>
       </c>
       <c r="G45" t="n">
-        <v>0.1637162142943989</v>
+        <v>0.05113929046032623</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.005758038962632895</v>
+        <v>-0.5412932863372792</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5972455379421756</v>
+        <v>-0.7885794676930494</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.602844556952267</v>
+        <v>-0.8580115371938982</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.03458834963719489</v>
+        <v>-0.0125287491470079</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.6672891863618813</v>
+        <v>-0.0500552754955073</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.197567727718341</v>
+        <v>-0.03408164546659376</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>71.23147029213553</v>
+        <v>61.7127852463605</v>
       </c>
       <c r="B46" t="n">
-        <v>60.83319734685846</v>
+        <v>52.01606418994763</v>
       </c>
       <c r="C46" t="n">
-        <v>46.07288569556869</v>
+        <v>45.63688227805158</v>
       </c>
       <c r="D46" t="n">
-        <v>5.908721266385168</v>
+        <v>7.97722647724349</v>
       </c>
       <c r="E46" t="n">
-        <v>2.50499578106149</v>
+        <v>2.367131805185632</v>
       </c>
       <c r="F46" t="n">
-        <v>7.308312671366617</v>
+        <v>6.096462548092147</v>
       </c>
       <c r="G46" t="n">
-        <v>0.04443592933768765</v>
+        <v>0.07448765032862179</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.6463171168696086</v>
+        <v>-0.3836925159072662</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.8314808476995151</v>
+        <v>-0.7282058380549568</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.8992384071404386</v>
+        <v>-0.7898158158977919</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.2335758163224712</v>
+        <v>-0.07290437838733253</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.7215598449644369</v>
+        <v>-0.2429180993666045</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.01367800752840184</v>
+        <v>-0.00271594926893326</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>86.83849224215936</v>
+        <v>94.21704756539961</v>
       </c>
       <c r="B47" t="n">
-        <v>123.142752804508</v>
+        <v>34.24984451237821</v>
       </c>
       <c r="C47" t="n">
-        <v>45.96947426970864</v>
+        <v>45.89891536259863</v>
       </c>
       <c r="D47" t="n">
-        <v>11.71210720419723</v>
+        <v>10.4751895930948</v>
       </c>
       <c r="E47" t="n">
-        <v>2.569643994314952</v>
+        <v>2.650801277197259</v>
       </c>
       <c r="F47" t="n">
-        <v>8.991238277636391</v>
+        <v>10.09711538396046</v>
       </c>
       <c r="G47" t="n">
-        <v>0.02268448174762997</v>
+        <v>0.0165901584829315</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.7994591688736404</v>
+        <v>-0.820492366938578</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8995438947838355</v>
+        <v>-0.9104632279891708</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.9523449499867273</v>
+        <v>-0.9589862168904864</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.05487392812641888</v>
+        <v>-0.006310934741807789</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.5236895922918156</v>
+        <v>-0.02194688057201688</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.005742007256051926</v>
+        <v>-0.06260922573682978</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>86.34582972432457</v>
+        <v>86.30602838422172</v>
       </c>
       <c r="B48" t="n">
-        <v>160.586942635326</v>
+        <v>191.4127490818646</v>
       </c>
       <c r="C48" t="n">
-        <v>45.96947426970864</v>
+        <v>46.24276578108098</v>
       </c>
       <c r="D48" t="n">
-        <v>11.71210720419723</v>
+        <v>12.12334264133981</v>
       </c>
       <c r="E48" t="n">
-        <v>2.571398917418399</v>
+        <v>2.408868781022476</v>
       </c>
       <c r="F48" t="n">
-        <v>8.911414852343039</v>
+        <v>9.038483957919693</v>
       </c>
       <c r="G48" t="n">
-        <v>0.02315184848172591</v>
+        <v>0.02277600513671729</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.7961202092124303</v>
+        <v>-0.7665079379120686</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.8979281100502589</v>
+        <v>-0.8837243007187761</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.9512914812540215</v>
+        <v>-0.941768102454291</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.04102659857895271</v>
+        <v>-0.004727804217591078</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.5200093689302616</v>
+        <v>-0.4899304522375796</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.005742007256051926</v>
+        <v>-0.1412036071042228</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>69.09436760299734</v>
+        <v>52.94490926175919</v>
       </c>
       <c r="B49" t="n">
-        <v>57.45375486097898</v>
+        <v>44.56049310362219</v>
       </c>
       <c r="C49" t="n">
-        <v>46.26447708330969</v>
+        <v>23.12627553122892</v>
       </c>
       <c r="D49" t="n">
-        <v>6.701815648017548</v>
+        <v>5.007057098008441</v>
       </c>
       <c r="E49" t="n">
-        <v>2.40265390055841</v>
+        <v>3.214753887052825</v>
       </c>
       <c r="F49" t="n">
-        <v>7.070251170235399</v>
+        <v>5.184812227246291</v>
       </c>
       <c r="G49" t="n">
-        <v>0.04980032464020186</v>
+        <v>0.1299838733731909</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.6131248914167362</v>
+        <v>-0.03155589599627743</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.8175104348676491</v>
+        <v>-0.6065074238381264</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.886494101262106</v>
+        <v>-0.6169780336348024</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.2448643112258443</v>
+        <v>-0.05420430051389173</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.7087908835026864</v>
+        <v>-0.4336602197980353</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.02302490623640506</v>
+        <v>-0.2413447566919116</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>50.53416302918475</v>
+        <v>97.94728834529944</v>
       </c>
       <c r="B50" t="n">
-        <v>61.75582964819927</v>
+        <v>181.0247441329589</v>
       </c>
       <c r="C50" t="n">
-        <v>40.74857079802572</v>
+        <v>46.5974709227448</v>
       </c>
       <c r="D50" t="n">
-        <v>5.000126076483163</v>
+        <v>10.62413647748887</v>
       </c>
       <c r="E50" t="n">
-        <v>2.592668247908154</v>
+        <v>2.650355033941866</v>
       </c>
       <c r="F50" t="n">
-        <v>4.778138860226974</v>
+        <v>10.82403058376221</v>
       </c>
       <c r="G50" t="n">
-        <v>0.1586772196864775</v>
+        <v>0.01450002544325413</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.02971203663519866</v>
+        <v>-0.8383951595882803</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.6053814262051251</v>
+        <v>-0.9188411266356288</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.6155092610460206</v>
+        <v>-0.9642359606700934</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.3343525142088645</v>
+        <v>-0.08849947896066192</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.6527267641486552</v>
+        <v>-0.5728744294602585</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.074153643497023</v>
+        <v>-0.2222790680559542</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>51.05912103030361</v>
+        <v>61.82023705434183</v>
       </c>
       <c r="B51" t="n">
-        <v>62.16163759334484</v>
+        <v>52.01873952681042</v>
       </c>
       <c r="C51" t="n">
-        <v>33.48886963889437</v>
+        <v>45.6309734563819</v>
       </c>
       <c r="D51" t="n">
-        <v>5.001102080405857</v>
+        <v>7.97722647724349</v>
       </c>
       <c r="E51" t="n">
-        <v>2.621740679413521</v>
+        <v>2.367131805185632</v>
       </c>
       <c r="F51" t="n">
-        <v>4.833325658995236</v>
+        <v>6.112973266035755</v>
       </c>
       <c r="G51" t="n">
-        <v>0.1525978636889201</v>
+        <v>0.07400354134433376</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.05890767526191949</v>
+        <v>-0.3868495900147974</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6152752184792781</v>
+        <v>-0.7293721003205376</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.6308045444097629</v>
+        <v>-0.7912446850426458</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.1227311150190062</v>
+        <v>-0.07862639475569606</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.6330288605207079</v>
+        <v>-0.2385528696673632</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.1664619181068022</v>
+        <v>-0.001365361458720432</v>
       </c>
     </row>
   </sheetData>
